--- a/AAII_Financials/Quarterly/GGAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GGAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
   <si>
     <t>GGAL</t>
   </si>
@@ -656,346 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1174700</v>
+        <v>1261800</v>
       </c>
       <c r="E8" s="3">
+        <v>1254300</v>
+      </c>
+      <c r="F8" s="3">
         <v>1292200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>912700</v>
       </c>
-      <c r="G8" s="3">
-        <v>1422600</v>
-      </c>
       <c r="H8" s="3">
-        <v>1423900</v>
+        <v>1703200</v>
       </c>
       <c r="I8" s="3">
+        <v>1893100</v>
+      </c>
+      <c r="J8" s="3">
         <v>2022100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1641600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2802300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3320400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4355300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4631000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6119600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5358900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>301600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>176100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>315000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>280100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>617100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>537700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>960000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>564600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>505800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>379200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1019300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>558800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>615700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>433600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>802100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>441600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>308800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>272200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>194300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>182800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>229300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>197700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>372300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>208700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>213100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>197300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>49400</v>
       </c>
       <c r="E9" s="3">
+        <v>49900</v>
+      </c>
+      <c r="F9" s="3">
         <v>56900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32300</v>
       </c>
-      <c r="G9" s="3">
-        <v>56300</v>
-      </c>
       <c r="H9" s="3">
-        <v>51300</v>
+        <v>69300</v>
       </c>
       <c r="I9" s="3">
+        <v>70800</v>
+      </c>
+      <c r="J9" s="3">
         <v>60900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>33900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>42800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>37800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>45700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>58800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>88400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>94100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1071,53 +1078,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1174700</v>
+        <v>1212500</v>
       </c>
       <c r="E10" s="3">
+        <v>1204300</v>
+      </c>
+      <c r="F10" s="3">
         <v>1235400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>880400</v>
       </c>
-      <c r="G10" s="3">
-        <v>1366300</v>
-      </c>
       <c r="H10" s="3">
-        <v>1372600</v>
+        <v>1634000</v>
       </c>
       <c r="I10" s="3">
+        <v>1822300</v>
+      </c>
+      <c r="J10" s="3">
         <v>1961100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1607700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2759500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3282600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4309500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4572200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6031200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5264800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1193,8 +1203,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1237,8 +1250,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1359,8 +1373,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1481,53 +1498,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-29200</v>
+        <v>-51000</v>
       </c>
       <c r="E14" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F14" s="3">
         <v>10500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10800</v>
       </c>
-      <c r="G14" s="3">
-        <v>-9200</v>
-      </c>
       <c r="H14" s="3">
-        <v>-29100</v>
+        <v>-9600</v>
       </c>
       <c r="I14" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="J14" s="3">
         <v>-47700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-20000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-62600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-168500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-33900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-150800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-77300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1603,130 +1623,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>54400</v>
+        <v>57600</v>
       </c>
       <c r="E15" s="3">
+        <v>51600</v>
+      </c>
+      <c r="F15" s="3">
         <v>55400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>118300</v>
       </c>
-      <c r="G15" s="3">
-        <v>11700</v>
-      </c>
       <c r="H15" s="3">
-        <v>52800</v>
+        <v>79000</v>
       </c>
       <c r="I15" s="3">
+        <v>76600</v>
+      </c>
+      <c r="J15" s="3">
         <v>77900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>57000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>53300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>71100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>152200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>42300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>33600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-10800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-6600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-13200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-12700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-29100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-26400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-51000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-29100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-45700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-24500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-32700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-16200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-8500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-10100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-21900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-16300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-7300</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1766,252 +1792,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1153800</v>
+        <v>1043300</v>
       </c>
       <c r="E17" s="3">
+        <v>1232000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1337900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1030100</v>
       </c>
-      <c r="G17" s="3">
-        <v>1175200</v>
-      </c>
       <c r="H17" s="3">
-        <v>1234200</v>
+        <v>1404300</v>
       </c>
       <c r="I17" s="3">
+        <v>1639900</v>
+      </c>
+      <c r="J17" s="3">
         <v>2063500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1310100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1796600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2754900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3708800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4117500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4783800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4726900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>293900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>156300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>227500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>430800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>350000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>696800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>385900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>416900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>297600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>651600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>384600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>448100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>394000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>779000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>410000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>265700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>200200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>130600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>107600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>128500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>109500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>220900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>124300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>131500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>20900</v>
+        <v>218500</v>
       </c>
       <c r="E18" s="3">
+        <v>22300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-45700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-117400</v>
       </c>
-      <c r="G18" s="3">
-        <v>247400</v>
-      </c>
       <c r="H18" s="3">
-        <v>189600</v>
+        <v>298900</v>
       </c>
       <c r="I18" s="3">
+        <v>253200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-41400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>331500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1005700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>565600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>646500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>513500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1335800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>632000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>87500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>79500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>186300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>187700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>263200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>178700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>88900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>81700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>367800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>174200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>167600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>39600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>23100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>31600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>43100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>72000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>63700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>75200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>100800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>88100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>151400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>84400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>81600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>62200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2054,252 +2087,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-300</v>
-      </c>
       <c r="H20" s="3">
-        <v>3700</v>
+        <v>-600</v>
       </c>
       <c r="I20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J20" s="3">
         <v>-901100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-12400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>30500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-63600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-51400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-80300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-76700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-116800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-128100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>15900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>32900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-40800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>28700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-65400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>23800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>341500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>212300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>43200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>20300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-8800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-16500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-12200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>74400</v>
+        <v>277700</v>
       </c>
       <c r="E21" s="3">
+        <v>72900</v>
+      </c>
+      <c r="F21" s="3">
         <v>14300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2200</v>
       </c>
-      <c r="G21" s="3">
-        <v>259400</v>
-      </c>
       <c r="H21" s="3">
-        <v>238700</v>
+        <v>378600</v>
       </c>
       <c r="I21" s="3">
+        <v>324900</v>
+      </c>
+      <c r="J21" s="3">
         <v>937600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>387100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1058800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>616200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>730000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>662500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1375500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>659500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>49300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>34800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>38900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>134800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>146700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>188500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>75500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>132100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>138000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>368900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>224900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>126700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>80400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>395000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>259300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>91100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>96600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>63600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>78200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>92200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>95400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>146400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>78300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>75700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>65100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2342,8 +2382,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2420,252 +2460,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>49200</v>
+        <v>271200</v>
       </c>
       <c r="E23" s="3">
+        <v>52500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-51600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-126900</v>
       </c>
-      <c r="G23" s="3">
-        <v>256900</v>
-      </c>
       <c r="H23" s="3">
-        <v>215000</v>
+        <v>309100</v>
       </c>
       <c r="I23" s="3">
+        <v>287200</v>
+      </c>
+      <c r="J23" s="3">
         <v>907400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>350100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1067200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>731300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>692700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>661100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1410500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>623500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>38200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>15300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>23900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>28000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>105900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>111000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>146400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>50600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>104800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>114500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>327000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>202900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>102300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>63400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>364600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>243900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>86300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>92300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>59500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>74000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>92000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>89100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>134900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>72100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>75400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>65000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1000</v>
+        <v>96800</v>
       </c>
       <c r="E24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-8100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-62900</v>
       </c>
-      <c r="G24" s="3">
-        <v>95600</v>
-      </c>
       <c r="H24" s="3">
-        <v>70800</v>
+        <v>115600</v>
       </c>
       <c r="I24" s="3">
+        <v>94500</v>
+      </c>
+      <c r="J24" s="3">
         <v>101800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>121900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>373500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>249900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>328300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>182500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>430100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>224700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>36900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>36800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>49300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>26300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>54700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>59200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>125400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>75300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>56800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>35600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>122700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>105200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>26300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>29000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>22800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>22700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>36200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>40500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>25800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>25600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2786,252 +2835,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>48100</v>
+        <v>174400</v>
       </c>
       <c r="E26" s="3">
+        <v>51400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-43500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-64000</v>
       </c>
-      <c r="G26" s="3">
-        <v>161300</v>
-      </c>
       <c r="H26" s="3">
-        <v>144300</v>
+        <v>193500</v>
       </c>
       <c r="I26" s="3">
+        <v>192700</v>
+      </c>
+      <c r="J26" s="3">
         <v>805600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>228200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>693700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>481500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>364400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>478600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>980400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>398900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>17200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>69000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>74200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>97100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>24400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>50100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>55400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>201600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>127600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>45400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>27800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>241900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>138700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>60000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>63200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>42400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>51200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>69300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>52900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>94400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>46400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>49900</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>48100</v>
+        <v>174400</v>
       </c>
       <c r="E27" s="3">
+        <v>51400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-43500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-64000</v>
       </c>
-      <c r="G27" s="3">
-        <v>161300</v>
-      </c>
       <c r="H27" s="3">
-        <v>144200</v>
+        <v>193500</v>
       </c>
       <c r="I27" s="3">
+        <v>192600</v>
+      </c>
+      <c r="J27" s="3">
         <v>805600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>228200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>693600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>481700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>364400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>478600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>980400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>398900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>12400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>17200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>69000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>74200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>97100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>49800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>54700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>198400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>124200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>43400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>28200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>241900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>138900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>60100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>61700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>48800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>65400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>48700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>88100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>42200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>46400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3152,8 +3210,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3229,8 +3290,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
@@ -3244,8 +3305,8 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -3254,28 +3315,31 @@
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>900</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
       <c r="AL29" s="3">
         <v>0</v>
       </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>-4300</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-4900</v>
       </c>
-      <c r="AO29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3396,8 +3460,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3518,252 +3585,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
-        <v>300</v>
-      </c>
       <c r="H32" s="3">
-        <v>-3700</v>
+        <v>600</v>
       </c>
       <c r="I32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J32" s="3">
         <v>901100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>12400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-30500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>63600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>51400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>80300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>76700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>116800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>128100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-32900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>40800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-28700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>65400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-23800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-341500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-212300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-43200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>8800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>16500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>12200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>6200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>48100</v>
+        <v>174400</v>
       </c>
       <c r="E33" s="3">
+        <v>51400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-43500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-64000</v>
       </c>
-      <c r="G33" s="3">
-        <v>161300</v>
-      </c>
       <c r="H33" s="3">
-        <v>144200</v>
+        <v>193500</v>
       </c>
       <c r="I33" s="3">
+        <v>192600</v>
+      </c>
+      <c r="J33" s="3">
         <v>805600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>228200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>693600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>481700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>364400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>478600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>980400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>398900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>12400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>17200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>69000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>74200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>97100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>49800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>54700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>198400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>124200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>43400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>28200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>241900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>138900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>60100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>61700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>49700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>65400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>48700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>83900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>37400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>46400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3884,257 +3960,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>48100</v>
+        <v>174400</v>
       </c>
       <c r="E35" s="3">
+        <v>51400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-43500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-64000</v>
       </c>
-      <c r="G35" s="3">
-        <v>161300</v>
-      </c>
       <c r="H35" s="3">
-        <v>144200</v>
+        <v>193500</v>
       </c>
       <c r="I35" s="3">
+        <v>192600</v>
+      </c>
+      <c r="J35" s="3">
         <v>805600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>228200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>693600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>481700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>364400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>478600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>980400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>398900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>12400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>17200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>69000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>74200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>97100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>49800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>54700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>198400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>124200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>43400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>28200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>241900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>138900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>60100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>61700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>49700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>65400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>48700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>83900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>37400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>46400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4177,8 +4262,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4221,297 +4307,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2189100</v>
+        <v>2583500</v>
       </c>
       <c r="E41" s="3">
+        <v>2969200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1731500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2930000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2268000</v>
       </c>
-      <c r="H41" s="3">
-        <v>2235800</v>
-      </c>
       <c r="I41" s="3">
+        <v>2178900</v>
+      </c>
+      <c r="J41" s="3">
         <v>3956400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4170800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1312300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2533000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3760900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1087800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1082200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>930700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>435200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>337200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>314700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>794400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1256700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>950800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>913000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1305300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1596900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1021300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1054800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1830200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1795500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1080100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1319800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1599000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1905000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1658600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1327500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>759000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1429900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>894100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>822600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1623000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1625000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>791700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2122900</v>
+        <v>2732700</v>
       </c>
       <c r="E42" s="3">
+        <v>2212500</v>
+      </c>
+      <c r="F42" s="3">
         <v>1716000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1110600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1389600</v>
       </c>
-      <c r="H42" s="3">
-        <v>1319800</v>
-      </c>
       <c r="I42" s="3">
+        <v>1376700</v>
+      </c>
+      <c r="J42" s="3">
         <v>1983900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1160400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2664500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>5191900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1436700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1155800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1069000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1518000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1249400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>904200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1677400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3195400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2345100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1987500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1985200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2493000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1936200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2250800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1268700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1821400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1463000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1953800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1924600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1466600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1014200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>256000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>229600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>2013000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>717600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>621300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>910600</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>226700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>320200</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>115600</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
         <v>38400</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3">
         <v>2119700</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3">
         <v>152800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1138200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>307000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>54000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>187400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>191900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>497600</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4587,52 +4680,55 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4709,53 +4805,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7600</v>
+        <v>853900</v>
       </c>
       <c r="E45" s="3">
+        <v>908500</v>
+      </c>
+      <c r="F45" s="3">
         <v>727800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>600000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>588200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>540100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>686500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>404500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>412500</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>558900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>345200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>363800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>329600</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4831,53 +4930,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>24760100</v>
+        <v>8929500</v>
       </c>
       <c r="E46" s="3">
+        <v>8713500</v>
+      </c>
+      <c r="F46" s="3">
         <v>8970400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8743900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9194900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7833600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11184300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8988800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6228600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2533000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11966000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4084100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3847600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4265900</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4953,8 +5055,11 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4962,365 +5067,374 @@
         <v>5133400</v>
       </c>
       <c r="E47" s="3">
+        <v>4980700</v>
+      </c>
+      <c r="F47" s="3">
         <v>4469000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3839200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4628200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6696000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8202700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3510200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4123900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>601700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6019100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5460500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6057700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5322600</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>3000</v>
       </c>
       <c r="R47" s="3">
         <v>3000</v>
       </c>
       <c r="S47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T47" s="3">
         <v>3100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>21100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>15300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>16300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>21800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>36100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>16700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>19200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>22000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>35000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>25600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>25100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>31100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7100</v>
-      </c>
-      <c r="AO47" s="3">
-        <v>1400</v>
       </c>
       <c r="AP47" s="3">
         <v>1400</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>921700</v>
+      </c>
+      <c r="E48" s="3">
         <v>942900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>823700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>853800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>948200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1024700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1270200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>759700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>717900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>633600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1038900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>670000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>681200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>668900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>120500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>110800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>96000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>200200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>342900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>246700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>229500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>305900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>411900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>288200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>316400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>349500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>461300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>142800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>147700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>173300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>147700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>154000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>146900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>163700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>333600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>101200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>98000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>336500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>100000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>91100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>287900</v>
+      </c>
+      <c r="E49" s="3">
         <v>293300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>262700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>258400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>286100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>300100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>388500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>252700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>242700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>221300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>361500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>219000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>228400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>221800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>40100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>37600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>33400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>69500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>216800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>83600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>76700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>101300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>259900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>95200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>104700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>97900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>121700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>56200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>51600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>52500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>50800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>16300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>15900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>17800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>102800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>71400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>65400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>91900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>67600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5441,8 +5555,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5563,130 +5680,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1782900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1132500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1221000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1712600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1041200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1441900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2085800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1534100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1073200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6214600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1446400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1232200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1213300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>972000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>23600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>45600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>97000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>39600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>28200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>30400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>39700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>46400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>33300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>13600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>17300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>15100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>13200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>13800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>149300</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AN52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO52" s="3">
         <v>46800</v>
       </c>
-      <c r="AO52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AP52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5807,130 +5930,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33994700</v>
+      </c>
+      <c r="E54" s="3">
         <v>32685300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31541400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30642800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31632200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32500900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>41585100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23838600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19130700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15572800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29874800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17902300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18930900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18181500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3520600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2965500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2618500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5177600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9257600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6361900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5789200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7319100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9964600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6906000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7617200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7752500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9615400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6766800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6853700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7681900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7670400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7580600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6216900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5415600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7508500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6294800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5807800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>6325800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>6342100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>5183700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5973,8 +6102,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6017,53 +6147,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>18514100</v>
+        <v>19594400</v>
       </c>
       <c r="E57" s="3">
+        <v>18349700</v>
+      </c>
+      <c r="F57" s="3">
         <v>18934500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17757100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17960300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17704700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23475700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13932700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9433200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7836100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16268800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10598000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11368200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10737900</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6118,74 +6249,77 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="3">
         <v>100600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>91900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>82000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>84500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>69700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>276400</v>
+        <v>1125200</v>
       </c>
       <c r="E58" s="3">
+        <v>784300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1684100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1480500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>592900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1086900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>878600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>133500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>127900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>253800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>288400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>284400</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6261,175 +6395,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>206000</v>
+        <v>785200</v>
       </c>
       <c r="E59" s="3">
+        <v>1016100</v>
+      </c>
+      <c r="F59" s="3">
         <v>768500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>842600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>912800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>335000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>904200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>327800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>288600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>1538400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>262600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>284600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>305500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>58000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>34900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>67600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>149200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>76400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>65400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>131800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>144400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>77800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>57600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>76200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>79700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>70300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>43100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>67400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>233500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>156700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>138800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>200700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>152000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>133300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>18996500</v>
+        <v>21626400</v>
       </c>
       <c r="E60" s="3">
+        <v>20344400</v>
+      </c>
+      <c r="F60" s="3">
         <v>21885900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20258200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19054900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18869600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26351400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15361800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10027500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7836100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18818400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11468900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12270800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11569100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6505,252 +6645,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2350900</v>
+        <v>4378400</v>
       </c>
       <c r="E61" s="3">
+        <v>4089300</v>
+      </c>
+      <c r="F61" s="3">
         <v>2910700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3102900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2717800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3744500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4850900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2552200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2124500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>629900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3521700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1722100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1876600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1860100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>415700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>346800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>316400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>642800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1184000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>756600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>655300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>879900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1242100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>749900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>792000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1137000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>944200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>706100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>721600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>755100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>396400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>538900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>434400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>270600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>291300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>599700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>576000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>287000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>599300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>536100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5111300</v>
+        <v>1771800</v>
       </c>
       <c r="E62" s="3">
+        <v>2025000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1370500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2096700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4039700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3497800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2468500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1275900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2759800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3240900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1573000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1020500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1194900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1069100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>28400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>50600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>71700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>66600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>61000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>59300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>85300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>109200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>117000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>83400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>119900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>25900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>24500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>25500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>24900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>23300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>18800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>18300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>31000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>14100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>12400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>33800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>10100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6871,8 +7020,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6993,8 +7145,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7115,130 +7270,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27786200</v>
+      </c>
+      <c r="E66" s="3">
         <v>26468200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26190100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25467600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25819100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26203400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33857700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19248900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14959500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11706900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23975800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14305500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15449300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14545300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2886800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2410200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2145300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4168800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7589600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5213600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4775400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6037300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8270500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5778000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6414400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6495200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8049800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5899400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6075800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6895700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6925700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6842200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5538600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4677100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6562900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5487400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5267600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5719600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5809300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4697200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7281,8 +7442,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7403,8 +7565,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7525,8 +7690,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7647,8 +7815,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7769,130 +7940,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3727800</v>
+      </c>
+      <c r="E72" s="3">
         <v>3702200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3178000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3177000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3533400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3935100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4769900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3039000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2717300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>-545600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2224300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2093200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2259500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>614000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>534500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>451000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>955800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2890400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1067600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>932900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1164800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2317700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1044500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1099600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1154600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1437500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>747900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>649100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>636700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>577500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>554000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>492800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>529300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>662100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>549800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>499000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>560000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>485800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>439400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8013,8 +8190,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8135,8 +8315,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8257,130 +8440,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6208300</v>
+      </c>
+      <c r="E76" s="3">
         <v>6216900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5351100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5175000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5812900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6297300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7727200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4589600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4171100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3865900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5898800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3596800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3481600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3636200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>633700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>555300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>473200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1008800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1667900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1148200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1013800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1281800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1694100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1128000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1202900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1257300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1565700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>867400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>777900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>786200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>744700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>738400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>678400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>738500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>945600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>807400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>540200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>606200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>532800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>486400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8501,257 +8690,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>48100</v>
+        <v>174400</v>
       </c>
       <c r="E81" s="3">
+        <v>51400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-43500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-64000</v>
       </c>
-      <c r="G81" s="3">
-        <v>161300</v>
-      </c>
       <c r="H81" s="3">
-        <v>144200</v>
+        <v>193500</v>
       </c>
       <c r="I81" s="3">
+        <v>192600</v>
+      </c>
+      <c r="J81" s="3">
         <v>805600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>228200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>693600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>481700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>364400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>478600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>980400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>398900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>12400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>17200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>69000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>74200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>97100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>49800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>54700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>198400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>124200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>43400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>28200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>241900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>138900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>60100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>61700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>49700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>65400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>48700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>83900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>37400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>46400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8794,130 +8992,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>34300</v>
+        <v>44900</v>
       </c>
       <c r="E83" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F83" s="3">
         <v>43300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>57000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>54200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>78100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>137100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>79700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>54700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>39700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8900</v>
-      </c>
-      <c r="S83" s="3">
-        <v>10900</v>
       </c>
       <c r="T83" s="3">
         <v>10900</v>
       </c>
       <c r="U83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="V83" s="3">
         <v>28800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>35700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>42100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>24800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>27200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>23500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>41900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>22000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>24500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>30400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>15400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>6300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>11500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>6100</v>
       </c>
-      <c r="AO83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AP83" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ83" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9038,8 +9240,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9160,8 +9365,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9282,8 +9490,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9404,8 +9615,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9526,130 +9740,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1883800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-158500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4293400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-608600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1167400</v>
-      </c>
       <c r="H89" s="3">
-        <v>-1345300</v>
+        <v>-1570500</v>
       </c>
       <c r="I89" s="3">
+        <v>-1784000</v>
+      </c>
+      <c r="J89" s="3">
         <v>-10561600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1936900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3838000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>216200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13584500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5331600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2704900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-424800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>114900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-61900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-191600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-591000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-387100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>576000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>234000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>34400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-163800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1135600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>475800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>453300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1290000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>339100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>211500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1181300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>260000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>201800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-351600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>353200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>46900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-420300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>15000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>629600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-160600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9692,130 +9912,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-71700</v>
       </c>
-      <c r="G91" s="3">
-        <v>17600</v>
-      </c>
       <c r="H91" s="3">
-        <v>-93800</v>
+        <v>-37500</v>
       </c>
       <c r="I91" s="3">
+        <v>-124400</v>
+      </c>
+      <c r="J91" s="3">
         <v>-101200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-186800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>59900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-63700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-101400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-110600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6910500</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-2714800</v>
       </c>
       <c r="S91" s="3">
         <v>-2714800</v>
       </c>
       <c r="T91" s="3">
+        <v>-2714800</v>
+      </c>
+      <c r="U91" s="3">
         <v>-2679600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7738000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5977500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3586400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-10600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-24200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9936,8 +10160,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10058,130 +10285,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-49500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-288800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29600</v>
       </c>
-      <c r="G94" s="3">
-        <v>-45500</v>
-      </c>
       <c r="H94" s="3">
-        <v>-67300</v>
+        <v>-61400</v>
       </c>
       <c r="I94" s="3">
+        <v>-89300</v>
+      </c>
+      <c r="J94" s="3">
         <v>1273400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-64600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-123000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-114500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-29100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>18600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-38100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-19100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-21300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-14200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-10500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10224,86 +10457,87 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>138100</v>
+      </c>
+      <c r="E96" s="3">
         <v>88500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>88600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>81100</v>
       </c>
-      <c r="G96" s="3">
-        <v>75000</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="H96" s="3">
+        <v>100200</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3">
         <v>57200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>254700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>551500</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3">
         <v>75500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>412500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>184800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>39100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-9500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-15200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-6900</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-11900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -10311,43 +10545,46 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-21200</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>1100</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>2100</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-7600</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>300</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10468,8 +10705,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10590,8 +10830,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10712,370 +10955,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1619800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1591000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2562500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2440500</v>
       </c>
-      <c r="G100" s="3">
-        <v>1934800</v>
-      </c>
       <c r="H100" s="3">
-        <v>392900</v>
+        <v>2587200</v>
       </c>
       <c r="I100" s="3">
+        <v>521100</v>
+      </c>
+      <c r="J100" s="3">
         <v>8340300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6950000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2610400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1839700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11215800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>8810400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2826900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>619800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>14700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>12100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>32800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>19700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>14200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-35900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-276900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-59200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>55700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-120100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-34000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-70300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-44300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-65200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>239100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>22700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>44600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>206700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>37200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>27800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>190300</v>
-      </c>
-      <c r="E101" s="3">
+        <v>750900</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3">
         <v>1377700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-282100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>371500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>97700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1144500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4340900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>488500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>372400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1777800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>951000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>563300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>309600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>80100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>60100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>57400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>47600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>74400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>87600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>171800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>145900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>31900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>132700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>223300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>104700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-86900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>784700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>181600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>213700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-85600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>358800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>214100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>45300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>61100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>21100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>35900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-27600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>27100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-95900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1799100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>528600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1372300</v>
       </c>
-      <c r="G102" s="3">
-        <v>1112800</v>
-      </c>
       <c r="H102" s="3">
-        <v>-829400</v>
+        <v>1706300</v>
       </c>
       <c r="I102" s="3">
+        <v>-1352200</v>
+      </c>
+      <c r="J102" s="3">
         <v>429800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4666400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-920800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2091700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3390100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7705200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>575600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>538400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>202600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-145800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-538200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-294800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>640200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>397100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>166600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>25100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-126000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>927300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>480000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>228000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-630000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>479900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>324700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>991800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>554900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>631600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-291800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>437500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>270200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-404200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>11800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>673900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-152300</v>
       </c>
     </row>
